--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -29,8 +29,11 @@
     <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14121,7 +14139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14241,6 +14259,23 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>CLUB_S2017_18_0151</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0031</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K228"/>
+  <dimension ref="A1:L228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14372,6 +14407,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14409,6 +14449,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: HC Kometa Brno.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14446,6 +14491,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14483,6 +14533,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14520,6 +14575,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14557,6 +14617,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14594,6 +14659,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14631,6 +14701,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14668,6 +14743,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14705,6 +14785,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14742,6 +14827,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14779,6 +14869,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14816,6 +14911,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14853,6 +14953,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14890,6 +14995,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14927,6 +15037,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14964,6 +15079,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15001,6 +15121,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15038,6 +15163,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15075,6 +15205,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15112,6 +15247,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15149,6 +15289,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15186,6 +15331,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15223,6 +15373,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15260,6 +15415,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15297,6 +15457,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15334,6 +15499,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15371,6 +15541,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15408,6 +15583,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15445,6 +15625,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15482,6 +15667,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15514,6 +15704,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15551,6 +15746,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15657,6 +15857,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0037</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15694,6 +15899,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0038</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15763,6 +15973,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0042</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15837,6 +16052,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0088</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -15874,6 +16094,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0099</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16461,6 +16686,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0062</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16974,6 +17204,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0075</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17418,6 +17653,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0088</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -17825,6 +18065,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0099</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -17862,6 +18107,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0100</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18005,6 +18255,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0102</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -18703,6 +18958,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0122</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -18994,6 +19254,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0130</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -19544,6 +19809,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0146</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -20025,6 +20295,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0159</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -20136,6 +20411,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0162</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -20242,6 +20522,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0165</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -20427,6 +20712,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0171</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -20538,6 +20828,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0172</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -21384,6 +21679,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0195</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -21786,6 +22086,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0203</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -22260,6 +22565,11 @@
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0216</t>
         </is>
       </c>
     </row>
@@ -39771,6 +40081,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -30754,6 +30754,11 @@
           <t>Draci Šumperk</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0066</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>30_2liga</t>
@@ -31845,6 +31850,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0109</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>30_Středočeský</t>
@@ -32711,6 +32721,11 @@
           <t>HC Spartak Žebrák</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0115</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>30_Středočeský</t>
@@ -33572,6 +33587,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0160</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>30_Plzeňský</t>
@@ -34841,6 +34861,11 @@
           <t>HCK Meteor</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0162</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>30_Plzeňský</t>
@@ -35217,6 +35242,11 @@
           <t>Jiskra Bezdružice</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0180</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>30_Plzeňský</t>
@@ -39029,6 +39059,11 @@
           <t>SKMB Boskovice</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0270</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr">
         <is>
           <t>30_Jihomoravský</t>
@@ -39588,6 +39623,11 @@
           <t>HC Bospor Bohumín</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0282</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
           <t>30_Severomoravský</t>
@@ -39774,6 +39814,11 @@
       <c r="C255" t="inlineStr">
         <is>
           <t>Wolves Český Těšín</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0286</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -14348,7 +14348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L228"/>
+  <dimension ref="A1:N228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14410,6 +14410,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -14496,6 +14496,16 @@
           <t>NODE_S2017_18_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14505,6 +14515,14 @@
         <is>
           <t>NODE_S2016_17_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -14580,6 +14598,16 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14589,6 +14617,14 @@
         <is>
           <t>NODE_S2016_17_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -14622,6 +14658,12 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14631,6 +14673,14 @@
         <is>
           <t>NODE_S2016_17_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -14664,6 +14714,16 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14673,6 +14733,14 @@
         <is>
           <t>NODE_S2016_17_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -14706,6 +14774,8 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14715,6 +14785,14 @@
         <is>
           <t>NODE_S2016_17_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -14748,6 +14826,8 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14757,6 +14837,14 @@
         <is>
           <t>NODE_S2016_17_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -14790,6 +14878,8 @@
           <t>NODE_S2017_18_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14799,6 +14889,14 @@
         <is>
           <t>NODE_S2016_17_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -14916,6 +15014,16 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14925,6 +15033,14 @@
         <is>
           <t>NODE_S2016_17_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14958,6 +15074,16 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14967,6 +15093,14 @@
         <is>
           <t>NODE_S2016_17_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -15000,6 +15134,12 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15009,6 +15149,14 @@
         <is>
           <t>NODE_S2016_17_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -15042,6 +15190,12 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15051,6 +15205,14 @@
         <is>
           <t>NODE_S2016_17_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -15084,6 +15246,8 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15093,6 +15257,14 @@
         <is>
           <t>NODE_S2016_17_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -15126,6 +15298,8 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15135,6 +15309,14 @@
         <is>
           <t>NODE_S2016_17_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -15420,6 +15602,12 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15429,6 +15617,14 @@
         <is>
           <t>NODE_S2016_17_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -15462,6 +15658,12 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15471,6 +15673,14 @@
         <is>
           <t>NODE_S2016_17_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -15504,6 +15714,12 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15513,6 +15729,14 @@
         <is>
           <t>NODE_S2016_17_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -15546,6 +15770,8 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15555,6 +15781,14 @@
         <is>
           <t>NODE_S2016_17_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -15588,6 +15822,8 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15597,6 +15833,14 @@
         <is>
           <t>NODE_S2016_17_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -16141,10 +16385,24 @@
           <t>NODE_S2017_18_0038</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0047</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -16326,10 +16584,24 @@
           <t>NODE_S2017_18_0038</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0050</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -16437,10 +16709,20 @@
           <t>NODE_S2017_18_0038</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -16770,10 +17052,24 @@
           <t>NODE_S2017_18_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0060</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -16807,10 +17103,24 @@
           <t>NODE_S2017_18_0057</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0065</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -16992,10 +17302,24 @@
           <t>NODE_S2017_18_0057</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0068</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -17103,10 +17427,20 @@
           <t>NODE_S2017_18_0057</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -17288,10 +17622,24 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0074</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -17325,10 +17673,24 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0077</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -17436,10 +17798,28 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0080</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0087</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -17547,10 +17927,20 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -17700,10 +18090,24 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0077</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -17811,10 +18215,20 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -17885,10 +18299,28 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0080</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0087</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -17996,10 +18428,20 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -18339,10 +18781,24 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0111</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -18487,10 +18943,20 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -18561,10 +19027,20 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -18672,10 +19148,24 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0111</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -18709,10 +19199,28 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0107</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0105</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="113">
@@ -18820,10 +19328,20 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -18894,10 +19412,20 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -19042,10 +19570,24 @@
           <t>NODE_S2017_18_0118</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0121</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -19079,10 +19621,24 @@
           <t>NODE_S2017_18_0118</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0124</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -19190,10 +19746,20 @@
           <t>NODE_S2017_18_0118</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -19338,10 +19904,24 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0129</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -19375,10 +19955,28 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0134</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0132</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="131">
@@ -19486,10 +20084,20 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -19560,10 +20168,20 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -19671,10 +20289,20 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="139">
@@ -19745,10 +20373,20 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="141">
@@ -19893,10 +20531,24 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0144</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -19930,10 +20582,24 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0147</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -20041,10 +20707,28 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0152</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0150</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="149">
@@ -20152,10 +20836,20 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="152">
@@ -20226,10 +20920,20 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -20379,10 +21083,24 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0144</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -20458,10 +21176,20 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -20606,10 +21334,24 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0168</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -20759,10 +21501,20 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="168">
@@ -20833,6 +21585,12 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0179</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20842,6 +21600,14 @@
         <is>
           <t>NODE_S2016_17_0172</t>
         </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -20949,10 +21715,28 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0176</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0174</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="173">
@@ -21060,10 +21844,20 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="176">
@@ -21134,10 +21928,20 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="178">
@@ -21245,10 +22049,24 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0171</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -21430,10 +22248,28 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0176</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0174</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="186">
@@ -21541,10 +22377,20 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="189">
@@ -21615,10 +22461,20 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="191">
@@ -21800,10 +22656,24 @@
           <t>NODE_S2017_18_0191</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0195</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -21837,10 +22707,28 @@
           <t>NODE_S2017_18_0191</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0200</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0198</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="197">
@@ -21948,10 +22836,20 @@
           <t>NODE_S2017_18_0191</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="200">
@@ -22022,10 +22920,20 @@
           <t>NODE_S2017_18_0191</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -22170,10 +23078,24 @@
           <t>NODE_S2017_18_0202</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0205</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -22207,10 +23129,24 @@
           <t>NODE_S2017_18_0202</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0210</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -22392,10 +23328,24 @@
           <t>NODE_S2017_18_0202</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0213</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -22503,10 +23453,20 @@
           <t>NODE_S2017_18_0202</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="215">
@@ -22651,10 +23611,24 @@
           <t>NODE_S2017_18_0215</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0218</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -22688,10 +23662,24 @@
           <t>NODE_S2017_18_0215</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0223</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -22873,10 +23861,24 @@
           <t>NODE_S2017_18_0215</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0226</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="225">
@@ -22984,10 +23986,20 @@
           <t>NODE_S2017_18_0215</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="228">

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -14663,7 +14663,6 @@
           <t>NODE_S2017_18_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14774,8 +14773,6 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14826,8 +14823,6 @@
           <t>NODE_S2017_18_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14878,8 +14873,6 @@
           <t>NODE_S2017_18_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15139,7 +15132,6 @@
           <t>NODE_S2017_18_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15195,7 +15187,6 @@
           <t>NODE_S2017_18_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15246,8 +15237,6 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15298,8 +15287,6 @@
           <t>NODE_S2017_18_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15607,7 +15594,6 @@
           <t>NODE_S2017_18_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15663,7 +15649,6 @@
           <t>NODE_S2017_18_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15719,7 +15704,6 @@
           <t>NODE_S2017_18_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15770,8 +15754,6 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15822,8 +15804,6 @@
           <t>NODE_S2017_18_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16390,7 +16370,6 @@
           <t>NODE_S2017_18_0047</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16589,7 +16568,6 @@
           <t>NODE_S2017_18_0050</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16709,8 +16687,6 @@
           <t>NODE_S2017_18_0038</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17057,7 +17033,6 @@
           <t>NODE_S2017_18_0060</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17108,7 +17083,6 @@
           <t>NODE_S2017_18_0065</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17307,7 +17281,6 @@
           <t>NODE_S2017_18_0068</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17427,8 +17400,6 @@
           <t>NODE_S2017_18_0057</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17627,7 +17598,6 @@
           <t>NODE_S2017_18_0074</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17678,7 +17648,6 @@
           <t>NODE_S2017_18_0077</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17927,8 +17896,6 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18095,7 +18062,6 @@
           <t>NODE_S2017_18_0077</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18215,8 +18181,6 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18428,8 +18392,6 @@
           <t>NODE_S2017_18_0071</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18786,7 +18748,6 @@
           <t>NODE_S2017_18_0111</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18943,8 +18904,6 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19027,8 +18986,6 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19153,7 +19110,6 @@
           <t>NODE_S2017_18_0111</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19328,8 +19284,6 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19412,8 +19366,6 @@
           <t>NODE_S2017_18_0099</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19575,7 +19527,6 @@
           <t>NODE_S2017_18_0121</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19626,7 +19577,6 @@
           <t>NODE_S2017_18_0124</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19746,8 +19696,6 @@
           <t>NODE_S2017_18_0118</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19909,7 +19857,6 @@
           <t>NODE_S2017_18_0129</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20084,8 +20031,6 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20168,8 +20113,6 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20289,8 +20232,6 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20373,8 +20314,6 @@
           <t>NODE_S2017_18_0126</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20536,7 +20475,6 @@
           <t>NODE_S2017_18_0144</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20587,7 +20525,6 @@
           <t>NODE_S2017_18_0147</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20836,8 +20773,6 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20920,8 +20855,6 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21088,7 +21021,6 @@
           <t>NODE_S2017_18_0144</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21176,8 +21108,6 @@
           <t>NODE_S2017_18_0141</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21339,7 +21269,6 @@
           <t>NODE_S2017_18_0168</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21501,8 +21430,6 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21590,7 +21517,6 @@
           <t>NODE_S2017_18_0179</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21844,8 +21770,6 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21928,8 +21852,6 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22054,7 +21976,6 @@
           <t>NODE_S2017_18_0171</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22377,8 +22298,6 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22461,8 +22380,6 @@
           <t>NODE_S2017_18_0160</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22661,7 +22578,6 @@
           <t>NODE_S2017_18_0195</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22836,8 +22752,6 @@
           <t>NODE_S2017_18_0191</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22920,8 +22834,6 @@
           <t>NODE_S2017_18_0191</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23083,7 +22995,6 @@
           <t>NODE_S2017_18_0205</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23134,7 +23045,6 @@
           <t>NODE_S2017_18_0210</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23333,7 +23243,6 @@
           <t>NODE_S2017_18_0213</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23453,8 +23362,6 @@
           <t>NODE_S2017_18_0202</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23616,7 +23523,6 @@
           <t>NODE_S2017_18_0218</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23667,7 +23573,6 @@
           <t>NODE_S2017_18_0223</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23866,7 +23771,6 @@
           <t>NODE_S2017_18_0226</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23986,8 +23890,6 @@
           <t>NODE_S2017_18_0215</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>complete</t>
@@ -41068,7 +40970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41140,6 +41042,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>4 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno</t>
         </is>
       </c>
     </row>

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -5266,7 +5266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7587,6 +7587,118 @@
       <c r="V39" s="2" t="n"/>
       <c r="W39" s="2" t="n"/>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0228</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0228</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0260</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0228</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0261</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00261</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7598,7 +7710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10430,6 +10542,545 @@
       <c r="V52" s="2" t="n"/>
       <c r="W52" s="2" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0229</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0229</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0262</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0229</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0263</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BK Havlíčkův Brod B</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0229</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0264</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>11</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0229</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0265</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0266</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0267</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0268</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0269</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0270</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0271</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Spartak Polička B</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0272</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00272</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10441,7 +11092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11344,6 +11995,362 @@
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0231</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>soutěž se nekoná</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0231</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0273</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0231</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0274</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0275</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0276</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0277</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0278</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0279</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2017_18_00279</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14348,7 +15355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N228"/>
+  <dimension ref="A1:N233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23938,6 +24945,191 @@
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Hradecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>REG_HKK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0141</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0160</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0160</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0191</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0191</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -28675,7 +29867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J259"/>
+  <dimension ref="A1:J279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -40956,6 +42148,546 @@
       <c r="J259" t="inlineStr">
         <is>
           <t>Nový Jičín</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0260</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>30HRAD</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0261</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>30HRAD</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0262</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0263</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0264</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>BK Havlíčkův Brod B</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>BK Havlíčkův Brod B</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0265</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0266</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0267</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0268</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0269</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0270</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0271</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0272</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Spartak Polička B</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Spartak Polička B</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0273</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>soutěž se nekoná</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>soutěž se nekoná</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0274</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0275</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0276</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0277</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0278</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0279</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -42800,7 +42811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42857,11 +42868,63 @@
           <t>NODE_S2017_18_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Hradecký – Krajská liga (Královéhradecký kraj) · NODE_S2017_18_0228</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (TJ Orli Lanškroun, HC Skuteč), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga (Vysočina) · NODE_S2017_18_0231</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (soutěž se nekoná, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15157,7 +15160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15292,6 +15295,40 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0228</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (TJ Orli Lanškroun, HC Skuteč), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0231</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (soutěž se nekoná, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -42888,7 +42925,7 @@
           <t>Hradecký – Krajská liga (Královéhradecký kraj) · NODE_S2017_18_0228</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (TJ Orli Lanškroun, HC Skuteč), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -42914,7 +42951,7 @@
           <t>Vysočina – Krajská liga (Vysočina) · NODE_S2017_18_0231</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (soutěž se nekoná, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -17123,7 +17123,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HC Lev Benešov – BK Mladá Boleslav "B"  7:1,2:6,4:1</t>
+          <t>HC Lev Benešov – BK Mladá Boleslav "B" 7:1,2:6,4:1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HC Čáslav – Slavoj Velké Popovice  0:4,3:2,3:2 PP</t>
+          <t>HC Čáslav – Slavoj Velké Popovice 0:4,3:2,3:2 PP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HC Junior Mělník – HK Lev Slaný  3:4 PP,2:3</t>
+          <t>HC Junior Mělník – HK Lev Slaný 3:4 PP,2:3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HC Rakovník – SK Černošice  5:4,4:7,3:5</t>
+          <t>HC Rakovník – SK Černošice 5:4,4:7,3:5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HC Lev Benešov – HK Lev Slaný  4:2,0:2,5:0</t>
+          <t>HC Lev Benešov – HK Lev Slaný 4:2,0:2,5:0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SK Černošice – HC Čáslav  5:1,3:2</t>
+          <t>SK Černošice – HC Čáslav 5:1,3:2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HC Lev Benešov – SK Černošice  3:6,5:6</t>
+          <t>HC Lev Benešov – SK Černošice 3:6,5:6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sokol Radomyšl – HC Milevsko 2010  2:6,5:2,4:5 PP</t>
+          <t>Sokol Radomyšl – HC Milevsko 2010 2:6,5:2,4:5 PP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HC Strakonice – HC Milevsko 2010  6:7,4:2,7:2</t>
+          <t>HC Strakonice – HC Milevsko 2010 6:7,4:2,7:2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HC Strakonice – Slavoj Český Krumlov  6:3,3:7,4:3 SN</t>
+          <t>HC Strakonice – Slavoj Český Krumlov 6:3,3:7,4:3 SN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HC Domažlice – HC Klatovy "B"  4:5,2:3 SN</t>
+          <t>HC Domažlice – HC Klatovy "B" 4:5,2:3 SN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HC Pubec Plzeň  - Sokol Malá Víska 0:5, 0:5 K</t>
+          <t>HC Pubec Plzeň - Sokol Malá Víska 0:5, 0:5 K</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Stadion Cheb – Čerti Ostrov  8:7,3:4 SN,5:6</t>
+          <t>Stadion Cheb – Čerti Ostrov 8:7,3:4 SN,5:6</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Stadion Cheb "B" – HC PSK 96 Cheb  8:6,6:4</t>
+          <t>Stadion Cheb "B" – HC PSK 96 Cheb 8:6,6:4</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mostečtí Lvi  - Slovan Louny 4:10,6:5,11:4</t>
+          <t>Mostečtí Lvi - Slovan Louny 4:10,6:5,11:4</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HC Turnov 1931 – HC Česká Lípa  5:4 PP,5:3</t>
+          <t>HC Turnov 1931 – HC Česká Lípa 5:4 PP,5:3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Slavoj Liberec – HC Česká Lípa  4:8,6:4,3:4 PP</t>
+          <t>Slavoj Liberec – HC Česká Lípa 4:8,6:4,3:4 PP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HC Turnov 1931  - HC Lomnice nad Popelkou 6:3,6:3</t>
+          <t>HC Turnov 1931 - HC Lomnice nad Popelkou 6:3,6:3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HC Jaroměř – HC Náchod  1:0 PP,3:6,2:0</t>
+          <t>HC Jaroměř – HC Náchod 1:0 PP,3:6,2:0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SK Třebechovice pod Orebem – HC Jaroměř  2:1 PP,4:2,3:1</t>
+          <t>SK Třebechovice pod Orebem – HC Jaroměř 2:1 PP,4:2,3:1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -22599,7 +22599,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Spartak Choceň - Spartak Polička  6:4,13:2</t>
+          <t>Spartak Choceň - Spartak Polička 6:4,13:2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22636,7 +22636,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou - BK Havlíčkův Brod B  4:1,4:6,1:2 PP</t>
+          <t>HC Světlá nad Sázavou - BK Havlíčkův Brod B 4:1,4:6,1:2 PP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HC Chrudim  - BK Havlíčkův Brod B  4:3,5:6 SN,6:3</t>
+          <t>HC Chrudim - BK Havlíčkův Brod B 4:3,5:6 SN,6:3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HC Chotěboř - Spartak Choceň  4:2,3:5,5:1</t>
+          <t>HC Chotěboř - Spartak Choceň 4:2,3:5,5:1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HC Chrudim  – HC Chotěboř 10:2,5:3</t>
+          <t>HC Chrudim – HC Chotěboř 10:2,5:3</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HC Chrudim – HC Litomyšl  5:2,3:4,2:4,6:0,1:3</t>
+          <t>HC Chrudim – HC Litomyšl 5:2,3:4,2:4,6:0,1:3</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -23090,7 +23090,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová  - HC Světlá nad Sázavou  8:4,2:3,7:2,5:4</t>
+          <t>Kohouti Česká Třebová - HC Světlá nad Sázavou 8:4,2:3,7:2,5:4</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HC Hlinsko - Spartak Choceň  7:1,4:3,7:6</t>
+          <t>HC Hlinsko - Spartak Choceň 7:1,4:3,7:6</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová  - HC Chotěboř 2:1 PP,5:1,2:1</t>
+          <t>Slovan Moravská Třebová - HC Chotěboř 2:1 PP,5:1,2:1</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -23256,7 +23256,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová  – HC Litomyšl  9:5,9:3,3:2</t>
+          <t>Kohouti Česká Třebová – HC Litomyšl 9:5,9:3,3:2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HC Hlinsko - Slovan Moravská Třebová  5:8,3:7,3:6</t>
+          <t>HC Hlinsko - Slovan Moravská Třebová 5:8,3:7,3:6</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová - Slovan Moravská Třebová  5:8,4:7,7:5,3:2 PP,3:4</t>
+          <t>Kohouti Česká Třebová - Slovan Moravská Třebová 5:8,4:7,7:5,3:2 PP,3:4</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -23494,7 +23494,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -23710,7 +23710,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí B  - TJ Náměšť nad Oslavou  3:8, 7:10</t>
+          <t>HHK Velké Meziříčí B - TJ Náměšť nad Oslavou 3:8, 7:10</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí B  - HC Zastávka  3:1,3:6,3:8</t>
+          <t>HHK Velké Meziříčí B - HC Zastávka 3:1,3:6,3:8</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BK Zubři Bystřice nad Pernštejnem - TJ Náměšť nad Oslavou  1:3,2:7</t>
+          <t>BK Zubři Bystřice nad Pernštejnem - TJ Náměšť nad Oslavou 1:3,2:7</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -24122,7 +24122,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SKMB Boskovice – HC Spartak Uherský Brod  4:2,5:3</t>
+          <t>SKMB Boskovice – HC Spartak Uherský Brod 4:2,5:3</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – HC Uherské Hradiště  5:3,5:1</t>
+          <t>HHK Velké Meziříčí – HC Uherské Hradiště 5:3,5:1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Hokej Uherský Ostroh – HK Kroměříž  2:3,5:8</t>
+          <t>Hokej Uherský Ostroh – HK Kroměříž 2:3,5:8</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HC Spartak Velká Bíteš – HC Uničov  2:7,2:4</t>
+          <t>HC Spartak Velká Bíteš – HC Uničov 2:7,2:4</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SKMB Boskovice – HK Kroměříž  6:5 PP,1:3,5:3,6:5 PP</t>
+          <t>SKMB Boskovice – HK Kroměříž 6:5 PP,1:3,5:3,6:5 PP</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -24476,7 +24476,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HC Orli Orlová 1930  - TJ Horní Benešov  7:1,6:3</t>
+          <t>HC Orli Orlová 1930 - TJ Horní Benešov 7:1,6:3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HC Bospor Bohumín – HC Frýdek Místek "B"  6:1,5:2</t>
+          <t>HC Bospor Bohumín – HC Frýdek Místek "B" 6:1,5:2</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HC Studénka – Wolves Český Těšín  5:3,5:6,6:5 SN</t>
+          <t>HC Studénka – Wolves Český Těšín 5:3,5:6,6:5 SN</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HC RT Torax Poruba 2011 "B" – HK Krnov  0:3,5:3,3:5</t>
+          <t>HC RT Torax Poruba 2011 "B" – HK Krnov 0:3,5:3,3:5</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HC Orli Orlová 1930  - HK Krnov  1:0 SN,2:3,4:3 SN</t>
+          <t>HC Orli Orlová 1930 - HK Krnov 1:0 SN,2:3,4:3 SN</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HC Bospor Bohumín – HC Studénka  3:9,4:6</t>
+          <t>HC Bospor Bohumín – HC Studénka 3:9,4:6</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -24967,7 +24967,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HC Orli Orlová 1930 – HC Studénka  5:1,1:4,2:6,2:12</t>
+          <t>HC Orli Orlová 1930 – HC Studénka 5:1,1:4,2:6,2:12</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">

--- a/data/S2017_18_FINAL.xlsx
+++ b/data/S2017_18_FINAL.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -25484,7 +25484,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -25557,7 +25557,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -25703,7 +25703,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -25922,7 +25922,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -26146,7 +26146,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -26292,7 +26292,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -26365,7 +26365,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -46262,7 +46262,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -57537,7 +57537,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -57610,7 +57610,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -57683,7 +57683,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -57756,7 +57756,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -57829,7 +57829,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -57902,7 +57902,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
